--- a/output/full_scan/batch_seq1_2026-07-09.xlsx
+++ b/output/full_scan/batch_seq1_2026-07-09.xlsx
@@ -5626,7 +5626,7 @@
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>249.0750819489134</v>
+        <v>249.0750819489133</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>14.7</v>

--- a/output/full_scan/batch_seq1_2026-07-09.xlsx
+++ b/output/full_scan/batch_seq1_2026-07-09.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>943.6940659102014</v>
+        <v>1113.694065910202</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>19.2</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.50579193718779</v>
+        <v>63.50579190070081</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>20.57220757959999</v>
+        <v>20.57220760396424</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1.969406591020142</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0986127215333848</v>
+        <v>0.0986127216001625</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1536</v>
+        <v>1216</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>751.3819355006322</v>
+        <v>1084.365503192129</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>55</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>62.61801578553827</v>
+        <v>66.13303635264342</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>15.0384174388999</v>
+        <v>31.09901061892101</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.238193550063211</v>
+        <v>1.221361326351165</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.6155314823283735</v>
+        <v>0.2966547411379387</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1303</v>
+        <v>1210</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>706.9178543101384</v>
+        <v>988.765219355396</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>181.5</v>
+        <v>57</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.33102505181893</v>
+        <v>59.56386340496472</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>40.52796464670723</v>
+        <v>40.60113326788829</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.693534600074097</v>
+        <v>0.5464185307449699</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.921361576973286</v>
+        <v>0.1209566904378657</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1314</v>
+        <v>1536</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>698.5306548683637</v>
+        <v>971.3819355006322</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8.9</v>
+        <v>55</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>55.71121363823953</v>
+        <v>62.61801570721476</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>37.63326105942583</v>
+        <v>15.0384174388999</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.685200762877836</v>
+        <v>4.238193550063211</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.1119336697385616</v>
+        <v>0.6155314822329776</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1210</v>
+        <v>1463</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>683.7652193553961</v>
+        <v>826.7426792127264</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>59.5638635037885</v>
+        <v>62.24492047459301</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>40.60113303991341</v>
+        <v>24.70130468245094</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.5464185307449699</v>
+        <v>1.491558393133662</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1209566901135154</v>
+        <v>0.0677854000685546</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1312</v>
+        <v>1303</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>678.7982275615402</v>
+        <v>821.9276965445682</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13.5</v>
+        <v>181.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>49.55178819962278</v>
+        <v>66.33102504972128</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>32.29314281237436</v>
+        <v>40.52796458375855</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.5420440970784713</v>
+        <v>1.69480126186641</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1099762651494238</v>
+        <v>0.9213615770305736</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1326</v>
+        <v>1468</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>666.428647857849</v>
+        <v>806.0556127927064</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>60</v>
+        <v>12.2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>55.14695652836455</v>
+        <v>57.04108722244205</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>28.20785631617622</v>
+        <v>16.46298973596019</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.173387238960465</v>
+        <v>0.7758248686300494</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,11 +888,11 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.5087735164866389</v>
+        <v>0.038343335401297</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>656.1375876044194</v>
+        <v>796.1375876044194</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>17.7</v>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.61787247780813</v>
+        <v>56.61787250695755</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>29.30506791853642</v>
+        <v>29.30506792234694</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0.5432190514848583</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0678651197691017</v>
+        <v>0.06786511975002291</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>636.2324222132964</v>
+        <v>778.5306548683637</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12.5</v>
+        <v>8.9</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>53.02356006262672</v>
+        <v>55.71121360771182</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>38.82458470842958</v>
+        <v>37.63326106270445</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.8706643917075441</v>
+        <v>1.685200762877836</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.0575637305546447</v>
+        <v>0.1119336697576417</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1216</v>
+        <v>1506</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>634.3655031921289</v>
+        <v>748.4965479196173</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>10.55</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>66.13303619727137</v>
+        <v>56.43758150516577</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>31.09901062278861</v>
+        <v>29.13540151948389</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.221361326351165</v>
+        <v>1.442041556138126</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,11 +1047,11 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.2966547411188603</v>
+        <v>0.0412713284349796</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, williams_r_recovery, cci_momentum</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>628.4614274814322</v>
+        <v>738.4614274814322</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>8.23</v>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>54.56541556646131</v>
+        <v>54.56541555403678</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>41.82555515273265</v>
+        <v>41.82555515031088</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0.5620891553043186</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0175203499405689</v>
+        <v>0.0175203499367533</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1506</v>
+        <v>1437</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>勤益控</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>608.4965479196175</v>
+        <v>737.3989283603677</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10.55</v>
+        <v>30.8</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>56.43758154002801</v>
+        <v>63.43552757745717</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>29.13540151948389</v>
+        <v>28.90640998911803</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.442041556138126</v>
+        <v>1.032317132461312</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.0412713284349796</v>
+        <v>0.0659353782852211</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, williams_r_recovery, cci_momentum</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1301</v>
+        <v>1423</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>利華</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>602.8543405502364</v>
+        <v>721.1672550630664</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>54.8</v>
+        <v>36.9</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>52.84227555498306</v>
+        <v>32.38796891003807</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>29.77050843903404</v>
+        <v>36.99431080552115</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.8509798996465073</v>
+        <v>0.0915477795769727</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.22880818768173</v>
+        <v>-0.1670299666921275</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1437</v>
+        <v>1256</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>勤益控</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>597.3989283603676</v>
+        <v>712.9258970767813</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>30.8</v>
+        <v>197.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>63.43552766796</v>
+        <v>63.73730410866992</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>28.90640987836528</v>
+        <v>21.08397671542742</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.032317132461312</v>
+        <v>1.815392334200346</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.06593537822798549</v>
+        <v>2.137379574139791</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>1463</v>
+        <v>1525</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>576.7426792127266</v>
+        <v>707.9115999257489</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>18</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>62.24492044259805</v>
+        <v>53.76677923642202</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>24.70130466799297</v>
+        <v>30.38667655819048</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.491558393133662</v>
+        <v>0.0384542610264535</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0677854001067149</v>
+        <v>0.1209835166895846</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1560</v>
+        <v>1563</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>巧新</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>573.6141732803125</v>
+        <v>706.5760650250492</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>709</v>
+        <v>67.7</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>50.55984248164593</v>
+        <v>57.73339222999726</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>19.71671339083866</v>
+        <v>39.1458001138043</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5918182851771989</v>
+        <v>0.9194699008809554</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-6.212029172141527</v>
+        <v>-0.116602256420351</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1513</v>
+        <v>1452</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>560.3510661748217</v>
+        <v>697.1900893003035</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>168.5</v>
+        <v>11.65</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>43.91051958328686</v>
+        <v>62.5329389262325</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>16.29674555642278</v>
+        <v>21.05072491179686</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.3549639909063835</v>
+        <v>0.6507940981625867</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-1.537171645566387</v>
+        <v>0.08926198801068649</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1468</v>
+        <v>1414</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>556.0556127927064</v>
+        <v>682.6803992920677</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>12.2</v>
+        <v>19.4</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>57.04108725769206</v>
+        <v>73.384201158981</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>16.4629896505079</v>
+        <v>30.79890066265265</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.7758248686300494</v>
+        <v>0.8841369357366652</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.038343335401297</v>
+        <v>0.1209926424754409</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1409</v>
+        <v>1326</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>551.8327766575335</v>
+        <v>666.428647857849</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>26.55</v>
+        <v>60</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>50.32581852745848</v>
+        <v>55.14695652621569</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>26.17592048444423</v>
+        <v>28.2078563287286</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.496690333059339</v>
+        <v>1.173387238960465</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.1627931887352973</v>
+        <v>0.50877351646756</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1525</v>
+        <v>1409</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>547.9115999257489</v>
+        <v>656.8327766575335</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>26.55</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>53.76677907506624</v>
+        <v>50.32581852202021</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>30.38667635085469</v>
+        <v>26.17592048143198</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.0384542610264535</v>
+        <v>1.496690333059339</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1209835169948526</v>
+        <v>-0.1627931886971381</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1414</v>
+        <v>1339</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>542.6803992920677</v>
+        <v>656.7483039399381</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>19.4</v>
+        <v>44.8</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>73.38420113071938</v>
+        <v>56.75512906047499</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>30.7989005633808</v>
+        <v>20.13822818488889</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8841369357366652</v>
+        <v>0.3526663370679664</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1209926424590916</v>
+        <v>0.0370916091981228</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1440</v>
+        <v>1227</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>542.1846164168699</v>
+        <v>653.9484955038132</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>13.35</v>
+        <v>29.75</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>48.47091405812992</v>
+        <v>56.70916262171151</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>24.14139446828774</v>
+        <v>24.96993313715051</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.8955070213751004</v>
+        <v>0.5530855484428122</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0035418308010054</v>
+        <v>0.0737753034818109</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>1563</v>
+        <v>1312</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>巧新</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>536.576065025049</v>
+        <v>653.7982275615401</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>67.7</v>
+        <v>13.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.73339226736162</v>
+        <v>49.55178817212606</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>39.14580011825395</v>
+        <v>32.29314276895951</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.9194699008809554</v>
+        <v>0.5420440970784713</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.116602256420351</v>
+        <v>-0.1099762651303435</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1466</v>
+        <v>1310</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>533.7582589359149</v>
+        <v>642.2288082458224</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>16.85</v>
+        <v>10.35</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>56.65751201120599</v>
+        <v>54.55956943888024</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>27.1799512540722</v>
+        <v>37.52524869326754</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.064573313040052</v>
+        <v>0.7796069837550225</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.3277118483384387</v>
+        <v>0.0727168022050972</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1452</v>
+        <v>1102</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>527.1900893003035</v>
+        <v>639.636954710881</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>11.65</v>
+        <v>35.7</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,49 +1824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>62.53293901720377</v>
+        <v>52.50614817917143</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>21.05072487625696</v>
+        <v>19.47555679184172</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6507940981625867</v>
+        <v>0.6177243193097125</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.08926198801068649</v>
+        <v>-0.012610496531535</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1339</v>
+        <v>1451</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>516.7483039399381</v>
+        <v>637.5646108969505</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>44.8</v>
+        <v>17.3</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>56.75512926530683</v>
+        <v>59.31762948649708</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>20.13822801045925</v>
+        <v>20.54207785730456</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.3526663370679664</v>
+        <v>0.6196276973876107</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0370916088356139</v>
+        <v>0.0361810800729562</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1227</v>
+        <v>1533</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>513.9484955038132</v>
+        <v>634.1692239747319</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>29.75</v>
+        <v>36.85</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.70916276279396</v>
+        <v>49.37843953906083</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>24.96993313715051</v>
+        <v>26.43761883652185</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5530855484428122</v>
+        <v>1.356328710423154</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.07377530338641219</v>
+        <v>-0.0605861870015075</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1310</v>
+        <v>1215</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>512.2288082458225</v>
+        <v>632.8989105370414</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>10.35</v>
+        <v>112</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.55956944890162</v>
+        <v>35.9041494025344</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>37.52524873831904</v>
+        <v>47.28294761500575</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7796069837550225</v>
+        <v>0.8700223042218407</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.07271680220319041</v>
+        <v>0.4990007921403299</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1460</v>
+        <v>1313</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>宏遠</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>510.3558592489514</v>
+        <v>626.2324222132964</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>7.17</v>
+        <v>12.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>46.83878893267873</v>
+        <v>53.02356003976045</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>24.58316053564481</v>
+        <v>38.82458468553233</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6979232316815985</v>
+        <v>0.8706643917075441</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0073950284575008</v>
+        <v>0.0575637305660928</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1540</v>
+        <v>1465</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>505.3421589363812</v>
+        <v>623.7464629279492</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>22.55</v>
+        <v>12.75</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>57.0815592888331</v>
+        <v>51.30343936975157</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>17.96458823860313</v>
+        <v>26.67970054045258</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.794211842184787</v>
+        <v>0.9143737505354848</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0512322173277545</v>
+        <v>0.0413902348184657</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1256</v>
+        <v>1531</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>492.9258970767813</v>
+        <v>621.7858910745124</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>197.5</v>
+        <v>13</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>63.73730406848593</v>
+        <v>55.36650942442417</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>21.08397663208704</v>
+        <v>18.7985896207492</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.815392334200346</v>
+        <v>1.350256656144896</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>2.137379574616773</v>
+        <v>0.009967946845023</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1503</v>
+        <v>1413</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>492.3328810077188</v>
+        <v>620.5535625328542</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>221.5</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>43.84420269422295</v>
+        <v>48.93998562413791</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>16.85659459498887</v>
+        <v>21.56157969006639</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4605809104562176</v>
+        <v>0.5723742180956563</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-3.003864270154454</v>
+        <v>-0.0005356318530626</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>1465</v>
+        <v>1460</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>宏遠</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>483.7464629279491</v>
+        <v>620.3558592489514</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>12.75</v>
+        <v>7.17</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>51.30343945423652</v>
+        <v>46.83878893772368</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>26.67970051668256</v>
+        <v>24.583160521006</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.9143737505354848</v>
+        <v>0.6979232316815985</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0413902347898463</v>
+        <v>0.0073950284575008</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1531</v>
+        <v>1540</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>481.7858910745125</v>
+        <v>620.3421589363812</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>13</v>
+        <v>22.55</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>55.36651008457194</v>
+        <v>57.08155913790321</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>18.79858959827046</v>
+        <v>17.96458824010251</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.350256656144896</v>
+        <v>0.794211842184787</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0099679468354835</v>
+        <v>0.0512322173277545</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1413</v>
+        <v>1321</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>480.5535625328542</v>
+        <v>615.5781734273053</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>9.390000000000001</v>
+        <v>31.45</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>48.9399856499882</v>
+        <v>55.11741271526976</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>21.56157965592403</v>
+        <v>29.10397466055836</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5723742180956563</v>
+        <v>0.5842894766061903</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.0005356318721422</v>
+        <v>0.0128569159474941</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1451</v>
+        <v>1477</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>聚陽</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>477.5646108969503</v>
+        <v>614.26193631809</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>17.3</v>
+        <v>222.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>59.31762965397758</v>
+        <v>49.79436085193025</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>20.54207783195848</v>
+        <v>16.55302988740336</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6196276973876107</v>
+        <v>0.5759842637592217</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0361810800157183</v>
+        <v>0.6657472074064161</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1321</v>
+        <v>1419</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>475.5781734273053</v>
+        <v>613.37448552486</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>31.45</v>
+        <v>66.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>55.11741292846931</v>
+        <v>53.98839418979191</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>29.10397420337961</v>
+        <v>18.58978836464784</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.5842894766061903</v>
+        <v>0.6451843961704021</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0128569157280754</v>
+        <v>0.0233243224612528</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1423</v>
+        <v>1219</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>利華</t>
+          <t>福壽</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>471.1672550630665</v>
+        <v>603.4331693424335</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>36.9</v>
+        <v>12.2</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>32.38796888299336</v>
+        <v>33.12888779087289</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>36.99431082341982</v>
+        <v>33.01962765819894</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.0915477795769727</v>
+        <v>1.856864452268636</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.1670299667684465</v>
+        <v>-0.0083034327524102</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1533</v>
+        <v>1301</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>464.169223974732</v>
+        <v>602.8543405502364</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>36.85</v>
+        <v>54.8</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>49.37843962317231</v>
+        <v>52.8422755448153</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>26.43761889360652</v>
+        <v>29.77050839678365</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.356328710423154</v>
+        <v>0.8509798996465073</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,11 +2584,11 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.0605861870301236</v>
+        <v>0.2288081877389709</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>459.9272456808016</v>
+        <v>599.9272456808014</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>28.45</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>59.11670640306819</v>
+        <v>59.11670592637483</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>21.02583298718789</v>
+        <v>21.02583313715729</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>0.3972321314651976</v>
@@ -2637,11 +2637,11 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.1116804959948596</v>
+        <v>0.111680496433683</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>459.0072655900709</v>
+        <v>574.0072655900708</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>10.55</v>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.92993271108546</v>
+        <v>51.9299325723448</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>24.91412198762546</v>
+        <v>24.91412200218916</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.4582034596263361</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.033310502215424</v>
+        <v>0.0333105022249636</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1342</v>
+        <v>1560</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>八貫</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>452.652551729501</v>
+        <v>573.6141732803126</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>110.5</v>
+        <v>709</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,49 +2725,49 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.36558063512764</v>
+        <v>50.55984250205866</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>30.70066282524245</v>
+        <v>19.7167133812358</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.1711548009571231</v>
+        <v>0.5918182851771989</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-1.001352610397019</v>
+        <v>-6.212029173858625</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1455</v>
+        <v>1514</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>集盛</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>449.6382027440224</v>
+        <v>572.0606630842238</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>122.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>44.27228911107415</v>
+        <v>49.54782898724779</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>40.56855442922161</v>
+        <v>16.20377457032028</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.163820274402243</v>
+        <v>0.5966699755463208</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.0612237510168123</v>
+        <v>-0.2474370119632739</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1419</v>
+        <v>1323</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>443.3744855248591</v>
+        <v>569.5704288850491</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>66.7</v>
+        <v>20.4</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>53.98839416567738</v>
+        <v>57.35366215837325</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>18.58978844332561</v>
+        <v>18.00829653000405</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6451843961704021</v>
+        <v>0.4590713102847115</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.023324321640842</v>
+        <v>0.0885554972730349</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1305</v>
+        <v>1342</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>八貫</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>440.8338839841819</v>
+        <v>567.6525517295011</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>12.8</v>
+        <v>110.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45.5683962012867</v>
+        <v>51.36558062323585</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>12.60644453832798</v>
+        <v>30.70066283346519</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.825329697142658</v>
+        <v>0.1711548009571231</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0113854884690117</v>
+        <v>-1.001352610435159</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1514</v>
+        <v>1308</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>432.060663084224</v>
+        <v>560.6109416799114</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>122.5</v>
+        <v>14.65</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.54782899574243</v>
+        <v>54.28964881425924</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>16.2037745830863</v>
+        <v>24.27213157503882</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5966699755463208</v>
+        <v>0.7826361435146814</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.2474370122494543</v>
+        <v>0.1101609230373785</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1229</v>
+        <v>1513</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>431.7444627124894</v>
+        <v>560.3510661748217</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>40.1</v>
+        <v>168.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>37.6199607216128</v>
+        <v>43.91051945067935</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>23.85926668069972</v>
+        <v>16.29674553137954</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6160537354127148</v>
+        <v>0.3549639909063835</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.2701558715798185</v>
+        <v>-1.537171644230782</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1308</v>
+        <v>1232</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>420.6109416799115</v>
+        <v>547.7934408833263</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>14.65</v>
+        <v>145.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>54.28964884509868</v>
+        <v>50.92860122895333</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>24.27213157503882</v>
+        <v>32.51435251649836</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.7826361435146814</v>
+        <v>0.9349808771376522</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1101609230278391</v>
+        <v>0.5815706073136573</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1102</v>
+        <v>1229</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>409.636954710881</v>
+        <v>546.7444627124895</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>35.7</v>
+        <v>40.1</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,49 +3096,49 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>52.50614822976009</v>
+        <v>37.6199606764544</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19.47555678654176</v>
+        <v>23.85926668511695</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6177243193097125</v>
+        <v>0.6160537354127148</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.0126104965601473</v>
+        <v>-0.2701558715607444</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1232</v>
+        <v>1517</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>407.7934408833264</v>
+        <v>545.3074938167103</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>145.5</v>
+        <v>10.7</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>50.9286011615024</v>
+        <v>52.65664869216462</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>32.51435246361246</v>
+        <v>25.04519374814751</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9349808771376522</v>
+        <v>0.4976749983063538</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.5815706075044734</v>
+        <v>0.0411034941418244</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1517</v>
+        <v>1532</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>405.3074938167103</v>
+        <v>544.1408854122022</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>10.7</v>
+        <v>23.05</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>52.65664869216462</v>
+        <v>54.03798698938113</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>25.04519372777409</v>
+        <v>28.8886293274988</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4976749983063538</v>
+        <v>0.3780022061474998</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0411034941609048</v>
+        <v>-0.06261460672154701</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1532</v>
+        <v>1440</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>404.1408854122022</v>
+        <v>542.1846164168699</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>23.05</v>
+        <v>13.35</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>54.0379870639944</v>
+        <v>48.47091388352582</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>28.88862934356075</v>
+        <v>24.14139481444811</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3780022061474998</v>
+        <v>0.8955070213751004</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0626146067406296</v>
+        <v>0.0035418309250238</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1323</v>
+        <v>1454</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>399.5704288850491</v>
+        <v>535.1156438627911</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>20.4</v>
+        <v>12.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>57.35366220021874</v>
+        <v>46.89685465462802</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>18.00829657262548</v>
+        <v>12.62385439953224</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4590713102847115</v>
+        <v>0.5747078981049503</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0885554972730349</v>
+        <v>0.0096587160973604</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>386.3090295745897</v>
+        <v>535.0368173357939</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>10.5</v>
+        <v>21.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.02405919327143</v>
+        <v>51.78072235182236</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>34.31959818971913</v>
+        <v>7.527261552479937</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.3313265251657873</v>
+        <v>0.2246701205506094</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0334707971679238</v>
+        <v>0.6168069097646642</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1217</v>
+        <v>1466</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>381.3833350938084</v>
+        <v>533.7582589359147</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>9.99</v>
+        <v>16.85</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>55.6148499179699</v>
+        <v>56.65751197947269</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>19.71449419800308</v>
+        <v>27.17995130212323</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6652388762369928</v>
+        <v>1.064573313040052</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0147496731139138</v>
+        <v>0.3277118483575172</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1568</v>
+        <v>1474</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>378.773364086476</v>
+        <v>526.3090295745897</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>32.9</v>
+        <v>10.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>38.28195166192706</v>
+        <v>54.02405925540382</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>25.067648858144</v>
+        <v>34.31959810301109</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.7178257860913142</v>
+        <v>0.3313265251657873</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-1.172846119512263</v>
+        <v>0.0334707971393045</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>福壽</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>378.4331693424335</v>
+        <v>521.3833350938083</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>12.2</v>
+        <v>9.99</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>33.12888802549412</v>
+        <v>55.6148499179699</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>33.01962753323163</v>
+        <v>19.71449419800308</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.856864452268636</v>
+        <v>0.6652388762369928</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0083034328096475</v>
+        <v>0.0147496731139138</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1236</v>
+        <v>1203</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>377.0800918959072</v>
+        <v>512.5887953800834</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>24.55</v>
+        <v>43.15</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>34.87020016855902</v>
+        <v>51.2557908616477</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13.79726263370302</v>
+        <v>10.37882334405148</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.461898599864744</v>
+        <v>1.085058195451758</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.07370030747796159</v>
+        <v>-0.0124775679124498</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1324</v>
+        <v>1459</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>376.0026107441666</v>
+        <v>511.2350605801228</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>10.45</v>
+        <v>11.65</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>48.61464605623445</v>
+        <v>45.63276768015094</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>22.82270688833133</v>
+        <v>16.89184132147494</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6979240178781463</v>
+        <v>1.195003541474975</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0099789392699095</v>
+        <v>0.0063633400857514</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1215</v>
+        <v>1410</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>372.8989105370414</v>
+        <v>510.6519954996294</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>112</v>
+        <v>26.25</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>35.90414956167118</v>
+        <v>53.63180401278096</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>47.28294759172861</v>
+        <v>22.43291794434261</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.8700223042218407</v>
+        <v>1.525710913117999</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.4990007914725467</v>
+        <v>0.2858870787083358</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1203</v>
+        <v>1443</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>372.5887953800835</v>
+        <v>500.6976930029215</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>43.15</v>
+        <v>26.1</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.25579103234542</v>
+        <v>46.72931010945141</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>10.37882329203672</v>
+        <v>15.82803002184752</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.085058195451758</v>
+        <v>0.9873642996974552</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0124775680555505</v>
+        <v>-0.1225730575088057</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1410</v>
+        <v>1476</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>370.6519954996294</v>
+        <v>499.9485892291045</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>26.25</v>
+        <v>335</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,49 +3785,49 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>53.63180397779652</v>
+        <v>53.00874129453841</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>22.43291794952155</v>
+        <v>18.028275184392</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.525710913117999</v>
+        <v>0.7493828293159801</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M63" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.285887078736953</v>
+        <v>2.40699373901022</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1402</v>
+        <v>1338</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>368.8900746581603</v>
+        <v>496.8166874580664</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>27.45</v>
+        <v>16.9</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45.09860713748015</v>
+        <v>50.02032540604765</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>17.11269830924475</v>
+        <v>17.98268078439923</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.011845243187736</v>
+        <v>0.5995218346247427</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.1738073233586915</v>
+        <v>0.0022701778641648</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1470</v>
+        <v>1503</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>365.036817335794</v>
+        <v>492.3328810077188</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>21.5</v>
+        <v>221.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>51.78072233974976</v>
+        <v>43.84420262148426</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>7.527261551021694</v>
+        <v>16.85659442443512</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.2246701205506094</v>
+        <v>0.4605809104562176</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.6168069098505216</v>
+        <v>-3.003864267006342</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1417</v>
+        <v>1324</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>362.691981447428</v>
+        <v>491.0026107441666</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>8.84</v>
+        <v>10.45</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>57.21562673935584</v>
+        <v>48.61464610602758</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>20.30700459399642</v>
+        <v>22.82270686818825</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.6431746677657226</v>
+        <v>0.6979240178781463</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.041038437791165</v>
+        <v>0.0099789392699095</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1445</v>
+        <v>1201</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>大宇</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>361.6980592992852</v>
+        <v>487.8761935308523</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>11.25</v>
+        <v>12.45</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>46.14545736193976</v>
+        <v>50.86786402745449</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>29.52397996057077</v>
+        <v>17.11376836444859</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5394376500921929</v>
+        <v>0.7279975884426462</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.06804841135260629</v>
+        <v>0.0157488115991878</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1477</v>
+        <v>1315</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>聚陽</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>359.26193631809</v>
+        <v>486.4480550024854</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>222.5</v>
+        <v>63.6</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>49.79436094686933</v>
+        <v>61.19546154285755</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16.55302978501444</v>
+        <v>18.9772459992071</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5759842637592217</v>
+        <v>0.7853998827761369</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.6657472071202319</v>
+        <v>0.1750897132918647</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1467</v>
+        <v>1402</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>358.8692978399006</v>
+        <v>484.3214690715218</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>8.41</v>
+        <v>27.45</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,49 +4103,49 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>58.07395426717926</v>
+        <v>45.09860705070972</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>26.16937757788881</v>
+        <v>17.11269830924475</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.7869297839900574</v>
+        <v>1.062584030526226</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.1139953673784448</v>
+        <v>-0.1738073233109895</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1338</v>
+        <v>1110</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>356.8166874580664</v>
+        <v>473.6095743767177</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>16.9</v>
+        <v>15.6</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>50.02032538363964</v>
+        <v>52.60818363337154</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.98268074158461</v>
+        <v>32.30140885827503</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5995218346247427</v>
+        <v>0.442062323141448</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0022701778737061</v>
+        <v>0.009980001257278701</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1315</v>
+        <v>1416</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>346.4480550024853</v>
+        <v>460.5785897033511</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>63.6</v>
+        <v>11.05</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>61.19546158094147</v>
+        <v>48.66895514341986</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>18.97724600593079</v>
+        <v>17.99144422963536</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7853998827761369</v>
+        <v>0.7019303632012567</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.1750897132537077</v>
+        <v>0.0264883037866371</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1110</v>
+        <v>1558</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>333.6095743767177</v>
+        <v>458.5250747492928</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>15.6</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>52.60818359828394</v>
+        <v>60.6316917055382</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>32.3014086828022</v>
+        <v>15.31570379495824</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.442062323141448</v>
+        <v>0.6409600476656153</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0099800012000404</v>
+        <v>0.2298137254712924</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1558</v>
+        <v>1526</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>318.525074749293</v>
+        <v>453.1550027125296</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>92.40000000000001</v>
+        <v>14.4</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>60.6316917055382</v>
+        <v>45.71798816170411</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.31570372621193</v>
+        <v>20.12087720712588</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6409600476656153</v>
+        <v>0.3823332647435687</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.229813725566685</v>
+        <v>0.0560778314336574</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1436</v>
+        <v>1455</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>集盛</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>315.1915487264786</v>
+        <v>449.6382027440224</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>44.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>42.73020275150076</v>
+        <v>44.27228911555009</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>14.26043309870944</v>
+        <v>40.56855442471186</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4092244428132172</v>
+        <v>1.163820274402243</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0582608622765835</v>
+        <v>-0.0612237510454324</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1539</v>
+        <v>1512</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>315.0676788093139</v>
+        <v>445.6175192949697</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>15.85</v>
+        <v>7.08</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>50.13112293557259</v>
+        <v>53.75812917015509</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.76521838192593</v>
+        <v>14.05900329811729</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.741956785619108</v>
+        <v>1.032613795629497</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0341826306097644</v>
+        <v>0.0409140632996309</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1526</v>
+        <v>1537</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>313.1550027125296</v>
+        <v>441.3290330902044</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>14.4</v>
+        <v>126</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45.71798808846666</v>
+        <v>49.93248874506551</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.12087718962256</v>
+        <v>19.7885399120103</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3823332647435687</v>
+        <v>0.6976276791960822</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0560778315099758</v>
+        <v>-0.0771407970091776</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1218</v>
+        <v>1539</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>307.7842263706779</v>
+        <v>430.0676788093138</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>16.85</v>
+        <v>15.85</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>22.02946056106201</v>
+        <v>50.131122770325</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>41.38674897652379</v>
+        <v>13.76521838725118</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.901794516785962</v>
+        <v>1.741956785619108</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0760001065232617</v>
+        <v>0.0341826306002246</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1537</v>
+        <v>1108</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>301.3290330902039</v>
+        <v>426.4042849303988</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>126</v>
+        <v>13.65</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>49.93248896022381</v>
+        <v>42.50082728479636</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19.78853966450965</v>
+        <v>21.53578061717455</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.6976276791960822</v>
+        <v>3.521668448386015</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.07714079729537469</v>
+        <v>0.0133835231683694</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1582</v>
+        <v>1305</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>298.0157882176666</v>
+        <v>425.8338839841819</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>79.2</v>
+        <v>12.8</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>33.30915263614619</v>
+        <v>45.5683961956555</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>23.44874406613573</v>
+        <v>12.60644451778666</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3356761363486149</v>
+        <v>0.825329697142658</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.3861420213147877</v>
+        <v>0.0113854884499322</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>295.0685303000388</v>
+        <v>425.1014319889357</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>15</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>29.14255809091908</v>
+        <v>51.23198846132122</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>28.34676242947242</v>
+        <v>25.72245293178362</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.956883364631385</v>
+        <v>0.1942269742953869</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.1343710363059846</v>
+        <v>0.0541063534867337</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1225</v>
+        <v>1472</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>291.4575708295671</v>
+        <v>419.2439503748232</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>28.1</v>
+        <v>88.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>37.64664557292265</v>
+        <v>49.84597412911443</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>20.58964607062542</v>
+        <v>11.45077539254488</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.1475176474907342</v>
+        <v>0.1078030077730213</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.2085572210969892</v>
+        <v>-0.2125563486589949</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1309</v>
+        <v>1319</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>286.4344550014859</v>
+        <v>415.5200309689265</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>14.55</v>
+        <v>75.8</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>44.31703771494185</v>
+        <v>37.27064326202172</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>12.44277527251579</v>
+        <v>29.5159319897209</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.7138303414173091</v>
+        <v>0.3289880092729073</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.09647389349301</v>
+        <v>-0.9863027363027684</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1108</v>
+        <v>1535</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>286.4042849303988</v>
+        <v>406.9579982006293</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>13.65</v>
+        <v>49.9</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>42.50082726486553</v>
+        <v>48.11971095844802</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>21.53578054658172</v>
+        <v>28.74780198637938</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>3.521668448386015</v>
+        <v>0.6132099833438779</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0133835231779098</v>
+        <v>-0.0075492071830545</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1459</v>
+        <v>1225</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>286.2350605801229</v>
+        <v>406.4575708295671</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>11.65</v>
+        <v>28.1</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45.63276771971099</v>
+        <v>37.64664557292265</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16.89184132147494</v>
+        <v>20.58964607062542</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.195003541474975</v>
+        <v>0.1475176474907342</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0063633400857514</v>
+        <v>-0.2085572210969892</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1454</v>
+        <v>1220</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>285.1156438627911</v>
+        <v>403.2318256991651</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>12.8</v>
+        <v>11.55</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46.89685460065957</v>
+        <v>40.11802452916537</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>12.6238543499617</v>
+        <v>23.58267988323589</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.5747078981049503</v>
+        <v>1.36206229765417</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0096587161259805</v>
+        <v>0.0188624864022615</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1441</v>
+        <v>1432</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>285.1014319889356</v>
+        <v>397.1516673265422</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>9.359999999999999</v>
+        <v>15.2</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>51.23198854919473</v>
+        <v>32.88651480676205</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>25.72245293178361</v>
+        <v>32.06310306946065</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.1942269742953869</v>
+        <v>0.2644648978697587</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0541063535058131</v>
+        <v>-0.0782431709385933</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1472</v>
+        <v>1109</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>279.2439503748232</v>
+        <v>389.0750819489134</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>88.5</v>
+        <v>14.7</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>49.8459744088249</v>
+        <v>51.4293449220183</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>11.45077512431552</v>
+        <v>14.84867794328212</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.1078030077730213</v>
+        <v>0.3862240370426066</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.2125563496129673</v>
+        <v>0.0322282002971549</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1307</v>
+        <v>1522</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>三芳</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>278.0947348785901</v>
+        <v>387.9633264186867</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>32.15</v>
+        <v>30</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>38.27723491782744</v>
+        <v>43.58536009578008</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19.69615293124372</v>
+        <v>12.18526599598892</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.621929998898142</v>
+        <v>0.4848503233038698</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.4947839662825252</v>
+        <v>-0.0368283679989737</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1512</v>
+        <v>1436</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>275.6175192949697</v>
+        <v>386.9763025711655</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>7.08</v>
+        <v>44.9</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>53.75812893535937</v>
+        <v>42.73020237531306</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>14.0590033215273</v>
+        <v>14.26043338113534</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.032613795629497</v>
+        <v>3.216448105367343</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0409140632652872</v>
+        <v>0.0582608626581773</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1319</v>
+        <v>1529</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>275.5200309689265</v>
+        <v>385.3323075874705</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>75.8</v>
+        <v>21.75</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>37.27064324551706</v>
+        <v>42.93616453008579</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>29.51593197484445</v>
+        <v>12.47942549375447</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.3289880092729073</v>
+        <v>1.361246407191476</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.9863027358257792</v>
+        <v>-0.065885878630949</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1201</v>
+        <v>1568</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>272.8761935308522</v>
+        <v>378.773364086476</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>12.45</v>
+        <v>32.9</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>50.86786409695177</v>
+        <v>38.28195164544822</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.11376836136407</v>
+        <v>25.06764891311234</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.7279975884426462</v>
+        <v>0.7178257860913142</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.015748811580108</v>
+        <v>-1.172846119474108</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1529</v>
+        <v>1521</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>270.3323075874702</v>
+        <v>378.158445311336</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>21.75</v>
+        <v>25.8</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>42.93616482270544</v>
+        <v>46.26696968556119</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.47942521426603</v>
+        <v>12.12747456103144</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.361246407191476</v>
+        <v>0.929009659546234</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0658858790697741</v>
+        <v>-0.048077090417162</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1535</v>
+        <v>1236</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>266.9579982006294</v>
+        <v>377.0800918959072</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>49.9</v>
+        <v>24.55</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>48.11971095844802</v>
+        <v>34.87020021349146</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>28.74780192411082</v>
+        <v>13.79726269571451</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.6132099833438779</v>
+        <v>1.461898599864744</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0075492072593775</v>
+        <v>-0.0737003074874984</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1438</v>
+        <v>1504</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>258.5330718796224</v>
+        <v>369.8546798097427</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>21.95</v>
+        <v>67.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>47.40061208254566</v>
+        <v>43.54374993482774</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.68718663375705</v>
+        <v>11.84468565613315</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.0501829628841008</v>
+        <v>0.7497839560183488</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.08058260288007379</v>
+        <v>-0.2453187263186548</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1432</v>
+        <v>1453</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>257.1516673265422</v>
+        <v>369.3725327465264</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>15.2</v>
+        <v>11.15</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>32.88651439722321</v>
+        <v>42.02445998548722</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>32.06310306946065</v>
+        <v>21.17761893919951</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.2644648978697587</v>
+        <v>0.6245414380393005</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0782431708622747</v>
+        <v>-0.0213023767953741</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1504</v>
+        <v>1417</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>254.8546798097427</v>
+        <v>362.6919814474281</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>67.5</v>
+        <v>8.84</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>43.5437499167197</v>
+        <v>57.21562672355111</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.84468553802065</v>
+        <v>20.30700459749601</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.7497839560183488</v>
+        <v>0.6431746677657226</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.2453187261660162</v>
+        <v>0.0410384377930721</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>大宇</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>250.6976930029216</v>
+        <v>361.6980592992853</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>26.1</v>
+        <v>11.25</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>46.72931003102568</v>
+        <v>46.14545733665134</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>15.82803001188104</v>
+        <v>29.52398000589316</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.9873642996974552</v>
+        <v>0.5394376500921929</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1225730574897263</v>
+        <v>0.06804841136214609</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>環泥</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>249.0750819489133</v>
+        <v>361.3910094537612</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>14.7</v>
+        <v>27.1</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>51.42934504450403</v>
+        <v>39.57546789750671</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>14.84867794328212</v>
+        <v>25.61539088436672</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3862240370426066</v>
+        <v>0.5284884332684721</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0322282002876151</v>
+        <v>-0.0368223258002853</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1522</v>
+        <v>1467</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>247.9633264186868</v>
+        <v>358.8692978399006</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>30</v>
+        <v>8.41</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>43.58536022918107</v>
+        <v>58.07395426272278</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>12.18526603611975</v>
+        <v>26.16937760513472</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.4848503233038698</v>
+        <v>0.7869297839900574</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0368283680371333</v>
+        <v>0.1139953673669973</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1456</v>
+        <v>1475</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>237.7867522919772</v>
+        <v>354.36135502326</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>13.35</v>
+        <v>27.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>38.2330558875454</v>
+        <v>53.62230450284744</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18.46108770070077</v>
+        <v>17.59927741997447</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.997856553822757</v>
+        <v>0.2894465310165504</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.1515361272929643</v>
+        <v>0.0015641358726241</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1304</v>
+        <v>1231</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>236.0661211264797</v>
+        <v>346.2687610923476</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>13.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>48.66592437744436</v>
+        <v>44.27189171248121</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>18.38953810744956</v>
+        <v>15.45048449358046</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6402440339436944</v>
+        <v>1.281988633345727</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0316565028725194</v>
+        <v>-0.1229593064772886</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1416</v>
+        <v>1569</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>235.5785897033512</v>
+        <v>326.8374707967399</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>11.05</v>
+        <v>47.45</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>48.66895509029267</v>
+        <v>45.52532367473083</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>17.99144421641121</v>
+        <v>15.45797120394773</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.7019303632012567</v>
+        <v>0.285751133351746</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0264883037961771</v>
+        <v>0.3097301706523201</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1231</v>
+        <v>1457</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>231.2687610923473</v>
+        <v>322.0535815238882</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>86.40000000000001</v>
+        <v>14.15</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>44.27189168330352</v>
+        <v>44.42869668626486</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15.45048450580876</v>
+        <v>14.23200610758492</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.281988633345727</v>
+        <v>0.5829436260606569</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.1229593063818898</v>
+        <v>0.0091943845919289</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1453</v>
+        <v>1516</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>229.3725327465264</v>
+        <v>321.8029313721378</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>11.15</v>
+        <v>18.2</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>42.02446006472456</v>
+        <v>29.93405557232731</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>21.17761888132101</v>
+        <v>39.28704843065594</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.6245414380393005</v>
+        <v>0.9273145696462732</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0213023767953741</v>
+        <v>-0.1353325695094281</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1528</v>
+        <v>1340</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>228.6348845319316</v>
+        <v>319.1755471951138</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>22.6</v>
+        <v>5.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>36.10846800029979</v>
+        <v>46.5460041452883</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>10.78142946268887</v>
+        <v>18.4032364807256</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.4901276701413371</v>
+        <v>0.8272132998122291</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1134445255869668</v>
+        <v>0.0276364596796816</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1104</v>
+        <v>1233</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>環泥</t>
+          <t>天仁</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>221.3910094537612</v>
+        <v>317.590341023081</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>27.1</v>
+        <v>27.9</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>39.57546798087925</v>
+        <v>45.41065059799767</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>25.61539087240147</v>
+        <v>9.60762911867889</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5284884332684721</v>
+        <v>0.7962556201381344</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0368223258575236</v>
+        <v>0.0049395625350528</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1521</v>
+        <v>1527</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>218.158445311336</v>
+        <v>316.9769916529456</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>25.8</v>
+        <v>33.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46.2669697792965</v>
+        <v>52.43906416240097</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.12747452280758</v>
+        <v>19.32662165500034</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.929009659546234</v>
+        <v>0.5249427044570961</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0480770904362399</v>
+        <v>0.0045655596661762</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1476</v>
+        <v>1439</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>214.9485892291044</v>
+        <v>312.0658046678985</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>335</v>
+        <v>23.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>53.0087413537032</v>
+        <v>40.12353522298393</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.02827517472432</v>
+        <v>13.54704484765578</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.7493828293159801</v>
+        <v>1.493694843997939</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>2.406993739296416</v>
+        <v>-0.0461671889751033</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1475</v>
+        <v>1524</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>214.36135502326</v>
+        <v>308.0143627911137</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>27.3</v>
+        <v>28.3</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>53.62230460712564</v>
+        <v>39.72033782970417</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>17.59927741602693</v>
+        <v>13.61395939724297</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.2894465310165504</v>
+        <v>0.4579933262057722</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0015641358821649</v>
+        <v>-0.0811575329384745</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1457</v>
+        <v>1218</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>207.0535815238882</v>
+        <v>307.784226370678</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>14.15</v>
+        <v>16.85</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>44.42869674253737</v>
+        <v>22.0294604501922</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14.23200600197573</v>
+        <v>41.38674904728708</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5829436260606569</v>
+        <v>1.901794516785962</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0091943845919289</v>
+        <v>-0.07600010648510309</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>1516</v>
+        <v>1538</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>正峰</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>206.8029313721378</v>
+        <v>306.0187093413904</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>18.2</v>
+        <v>10</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>29.93405566135608</v>
+        <v>51.65186275143267</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>39.2870484168044</v>
+        <v>6.889464855848405</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.9273145696462732</v>
+        <v>0.4761769199381293</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1353325695571273</v>
+        <v>0.4176696722779589</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1233</v>
+        <v>1101</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>天仁</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>202.5903410230811</v>
+        <v>304.4542034463151</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>27.9</v>
+        <v>22.7</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>45.41065058712579</v>
+        <v>33.81966209780737</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>9.60762913321653</v>
+        <v>13.40661287129065</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.7962556201381344</v>
+        <v>1.234062358958489</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0049395625445894</v>
+        <v>-0.1256535207654591</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1519</v>
+        <v>1582</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>197.5773700139854</v>
+        <v>298.0157882176666</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>721</v>
+        <v>79.2</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>33.33572989070983</v>
+        <v>33.30915259052078</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>14.78621266525504</v>
+        <v>23.4487440481746</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.7215365296880457</v>
+        <v>0.3356761363486149</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-4.97017710025446</v>
+        <v>-0.3861420211621515</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>1439</v>
+        <v>1325</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>197.0658046678984</v>
+        <v>296.6401430676227</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>23.5</v>
+        <v>24.45</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>40.12353521803108</v>
+        <v>38.42409673629061</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.54704485624218</v>
+        <v>21.8114949470432</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.493694843997939</v>
+        <v>0.3769587943995452</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0461671889464865</v>
+        <v>-0.0069858844422181</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1524</v>
+        <v>1446</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>193.0143627911137</v>
+        <v>295.0685303000386</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>28.3</v>
+        <v>15</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>39.72033789865189</v>
+        <v>29.14255798303364</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>13.61395945979065</v>
+        <v>28.34676261132962</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.4579933262057722</v>
+        <v>1.956883364631385</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0811575329003143</v>
+        <v>-0.1343710362487455</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1101</v>
+        <v>1541</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>189.4542034463151</v>
+        <v>294.6971837649248</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>22.7</v>
+        <v>21.4</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>33.81966213306767</v>
+        <v>46.94623400143674</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>13.40661289604155</v>
+        <v>10.52492005393416</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.234062358958489</v>
+        <v>0.4056260632219113</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.1256535207654591</v>
+        <v>0.009573651168938799</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1569</v>
+        <v>1530</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>186.83747079674</v>
+        <v>289.3647616184241</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>47.45</v>
+        <v>28.75</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>45.525323772716</v>
+        <v>43.64647800406218</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>15.45797119194736</v>
+        <v>15.4303230007712</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.285751133351746</v>
+        <v>0.5202533784017054</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.3097301706141644</v>
+        <v>-0.1013414599853024</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1220</v>
+        <v>1309</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>178.2318256991651</v>
+        <v>286.4344550014859</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>11.55</v>
+        <v>14.55</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>40.11802439103871</v>
+        <v>44.31703770644711</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>23.58267988468268</v>
+        <v>12.44277527251578</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.36206229765417</v>
+        <v>0.7138303414173091</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0188624864213408</v>
+        <v>0.0964738934834688</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1527</v>
+        <v>1316</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>176.9769916529456</v>
+        <v>278.5545641267022</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>33.5</v>
+        <v>10.35</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>52.4390641845241</v>
+        <v>44.95692449072561</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>19.32662167930086</v>
+        <v>12.05211609154889</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5249427044570961</v>
+        <v>0.3081760768925539</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.0045655596661762</v>
+        <v>0.0018744537992093</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1471</v>
+        <v>1307</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>首利</t>
+          <t>三芳</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>175.60302052145</v>
+        <v>278.0947348785901</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>10.4</v>
+        <v>32.15</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>42.73673540033512</v>
+        <v>38.27723484998986</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>9.928759559719678</v>
+        <v>19.69615294666976</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.2859919077109487</v>
+        <v>0.621929998898142</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0385902915577886</v>
+        <v>-0.4947839662539095</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1316</v>
+        <v>1103</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>163.5545641267023</v>
+        <v>276.2595550468587</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>10.35</v>
+        <v>13.4</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>44.9569245418021</v>
+        <v>46.12390586724697</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>12.05211609154889</v>
+        <v>11.93610771225878</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.3081760768925539</v>
+        <v>1.071855938902817</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0018744537896707</v>
+        <v>-0.0196552288446087</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1325</v>
+        <v>1341</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>156.6401430676208</v>
+        <v>261.6313543444667</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>24.45</v>
+        <v>58.2</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>38.42409630839713</v>
+        <v>50.87808533662371</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>21.8114949192112</v>
+        <v>18.70547808128196</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.3769587943995452</v>
+        <v>0.5742337125468548</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.006985884575775</v>
+        <v>0.4922851440930578</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1541</v>
+        <v>1438</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>154.6971837649248</v>
+        <v>258.5330718796224</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>21.4</v>
+        <v>21.95</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>46.94623412733149</v>
+        <v>47.40061203945261</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>10.52492005393416</v>
+        <v>16.68718663222937</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.4056260632219113</v>
+        <v>0.0501829628841008</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.009573651168938799</v>
+        <v>-0.0805826029563927</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1530</v>
+        <v>1456</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>149.3647616184241</v>
+        <v>237.7867522919772</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>28.75</v>
+        <v>13.35</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>43.64647796374681</v>
+        <v>38.23305586518425</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>15.43032299097756</v>
+        <v>18.46108763879914</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.5202533784017054</v>
+        <v>1.997856553822757</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.1013414599376035</v>
+        <v>-0.1515361273311232</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1340</v>
+        <v>1304</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>149.1755471951137</v>
+        <v>236.0661211264794</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>5.5</v>
+        <v>13.4</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>46.54600422656866</v>
+        <v>48.66592437744436</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>18.40323629422011</v>
+        <v>18.38953806786542</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.8272132998122291</v>
+        <v>0.6402440339436944</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0276364596682337</v>
+        <v>0.0316565028629801</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1213</v>
+        <v>1473</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>137.7315302184456</v>
+        <v>232.2701054155521</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>7.53</v>
+        <v>20.2</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>48.83168042049857</v>
+        <v>45.01480065703494</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>5.457368944269051</v>
+        <v>19.05925752205437</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.3145700967647647</v>
+        <v>0.5935295184631811</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0060805645461615</v>
+        <v>0.0759059250720399</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1103</v>
+        <v>1528</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>136.2595550468587</v>
+        <v>228.6348845319316</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>13.4</v>
+        <v>22.6</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>46.12390589379934</v>
+        <v>36.10846797229728</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>11.93610768411192</v>
+        <v>10.78142946568979</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>1.071855938902817</v>
+        <v>0.4901276701413371</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.019655228863688</v>
+        <v>-0.1134445255678873</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1473</v>
+        <v>1519</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>117.2701054155521</v>
+        <v>197.5773700139853</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>20.2</v>
+        <v>721</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>45.01480078181318</v>
+        <v>33.33572985631641</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>19.0592575442391</v>
+        <v>14.7862126494285</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.5935295184631811</v>
+        <v>0.7215365296880457</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.0759059250338812</v>
+        <v>-4.970177100063687</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1538</v>
+        <v>1471</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>正峰</t>
+          <t>首利</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>106.0187093413903</v>
+        <v>175.60302052145</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>51.65186195362522</v>
+        <v>42.73673519310378</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>6.889464501159459</v>
+        <v>9.928759766086594</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.4761769199381293</v>
+        <v>0.2859919077109487</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.4176696778109993</v>
+        <v>-0.0385902914242324</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1341</v>
+        <v>1213</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>61.63135434446669</v>
+        <v>137.7315302184456</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>58.2</v>
+        <v>7.53</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>50.87808533376011</v>
+        <v>48.83168033381035</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>18.70547808128196</v>
+        <v>5.45736905887305</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.5742337125468548</v>
+        <v>0.3145700967647647</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,11 +7354,11 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.4922851440930578</v>
+        <v>0.0060805645557013</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
